--- a/task-reviews/graph/task_graph_path_shortest_path_length/task_graph_path_shortest_path_length.xlsx
+++ b/task-reviews/graph/task_graph_path_shortest_path_length/task_graph_path_shortest_path_length.xlsx
@@ -155,9 +155,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -183,9 +180,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -211,9 +205,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -239,9 +230,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -267,9 +255,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -295,9 +280,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -323,9 +305,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -351,9 +330,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -379,9 +355,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -407,9 +380,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -435,9 +405,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -463,9 +430,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -491,9 +455,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -519,9 +480,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -547,9 +505,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -575,9 +530,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -603,9 +555,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -631,9 +580,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -659,9 +605,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -687,9 +630,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -715,9 +655,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -743,9 +680,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -771,9 +705,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -799,9 +730,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -827,9 +755,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -855,9 +780,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -883,9 +805,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -911,9 +830,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -939,9 +855,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -967,9 +880,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -995,9 +905,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1023,9 +930,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1051,9 +955,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1079,9 +980,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1107,9 +1005,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1135,9 +1030,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1163,9 +1055,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1191,9 +1080,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1219,9 +1105,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1247,9 +1130,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1275,9 +1155,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1303,9 +1180,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1331,9 +1205,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1359,9 +1230,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1387,9 +1255,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1415,9 +1280,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1443,9 +1305,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1471,9 +1330,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1499,9 +1355,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1527,9 +1380,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1560,9 +1410,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1588,9 +1435,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1616,9 +1460,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1644,9 +1485,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1672,9 +1510,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1700,9 +1535,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1728,9 +1560,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1756,9 +1585,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1784,9 +1610,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1812,9 +1635,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1840,9 +1660,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1868,9 +1685,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1896,9 +1710,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1924,9 +1735,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1952,9 +1760,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1980,9 +1785,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2008,9 +1810,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2036,9 +1835,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2064,9 +1860,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2092,9 +1885,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2120,9 +1910,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2148,9 +1935,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2176,9 +1960,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2204,9 +1985,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2232,9 +2010,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2260,9 +2035,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2288,9 +2060,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2316,9 +2085,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2344,9 +2110,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2372,9 +2135,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2400,9 +2160,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2428,9 +2185,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2456,9 +2210,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2484,9 +2235,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2512,9 +2260,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2540,9 +2285,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2568,9 +2310,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2596,9 +2335,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2624,9 +2360,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2652,9 +2385,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2680,9 +2410,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2708,9 +2435,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2736,9 +2460,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2764,9 +2485,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2792,9 +2510,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2820,9 +2535,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2848,9 +2560,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2876,9 +2585,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2904,9 +2610,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2932,9 +2635,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3329,31 +3029,31 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Question: The directed graph has a unique shortest path from node A to node B, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node 1 to node 2, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node A to node B, including both endpoints.
-Answer: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
+Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node 1 to node 2, including both endpoints.
+Answer requirement: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Question: The directed graph has a unique shortest path from node A to node B, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node 1 to node 2, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of edges in that path as an integer.
+Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["A", "D", "E", "F", "B"], "answer": 4}</t>
+          <t>{"evidence": ["1", "2"], "answer": 1}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>["A", "D", "E", "F", "B"]</t>
+          <t>["1", "2"]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3367,16 +3067,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>34356124649959</v>
+        <v>345563621719163</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0021.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0009.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0021.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0009.json</t>
         </is>
       </c>
     </row>
@@ -3393,31 +3093,31 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled directed graph. Task: The directed graph has a unique shortest path from node E to node B, following the direction of the arrows. How many edges are in that path?
+          <t>Use the image containing a labeled directed graph. The directed graph has a unique shortest path from node D to node F, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node B, including both endpoints.
-Answer requirement: set "answer" to the number of edges in that path as an integer.
+Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node D to node F, including both endpoints.
+Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["B","D","H"],"answer":2}</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled directed graph. Task: The directed graph has a unique shortest path from node E to node B, following the direction of the arrows. How many edges are in that path?
+          <t>Use the image containing a labeled directed graph. The directed graph has a unique shortest path from node D to node F, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of edges in that path as an integer.
+Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["E", "D", "A", "B"], "answer": 3}</t>
+          <t>{"evidence": ["D", "B", "A", "G", "C", "F"], "answer": 5}</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>["E", "D", "A", "B"]</t>
+          <t>["D", "B", "A", "G", "C", "F"]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -3431,16 +3131,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>228561350480058</v>
+        <v>819076031830887</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0019.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0017.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0019.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0017.json</t>
         </is>
       </c>
     </row>
@@ -3457,31 +3157,31 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node 3 to node 2, following the direction of the arrows. How many edges are in that path?
+          <t>Look at the image with a labeled directed graph. Task: The directed graph has a unique shortest path from node E to node C, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node 3 to node 2, including both endpoints.
-Answer: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["2","5","8"],"answer":2}</t>
+Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node C, including both endpoints.
+Answer format: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["B","D","H"],"answer":2}</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node 3 to node 2, following the direction of the arrows. How many edges are in that path?
+          <t>Look at the image with a labeled directed graph. Task: The directed graph has a unique shortest path from node E to node C, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of edges in that path as an integer.
+Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["3", "2"], "answer": 1}</t>
+          <t>{"evidence": ["E", "G", "A", "C"], "answer": 3}</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>["3", "2"]</t>
+          <t>["E", "G", "A", "C"]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3495,16 +3195,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1109607556103476</v>
+        <v>1003087918148462</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0014.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0010.png</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0014.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0010.json</t>
         </is>
       </c>
     </row>
@@ -3521,17 +3221,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node G to node F, following the direction of the arrows. How many edges are in that path?
+          <t>Use the image containing a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node 2 to node 1, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node G to node F, including both endpoints.
-Answer rule: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
+Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node 2 to node 1, including both endpoints.
+Answer format: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node G to node F, following the direction of the arrows. How many edges are in that path?
+          <t>Use the image containing a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node 2 to node 1, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the number of edges in that path as an integer.
 Example JSON:
@@ -3540,12 +3240,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["G", "E", "D", "A", "B", "F"], "answer": 5}</t>
+          <t>{"evidence": ["2", "6", "5", "4", "1"], "answer": 4}</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>["G", "E", "D", "A", "B", "F"]</t>
+          <t>["2", "6", "5", "4", "1"]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3559,16 +3259,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1337491737120166</v>
+        <v>1396546905279918</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0023.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0005.png</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0023.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0005.json</t>
         </is>
       </c>
     </row>
@@ -3585,31 +3285,31 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Question: The directed graph has a unique shortest path from node 4 to node 2, following the direction of the arrows. How many edges are in that path?
+          <t>Look at the image with a labeled directed graph. Question: The directed graph has a unique shortest path from node D to node F, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node 4 to node 2, including both endpoints.
-Answer requirement: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["2","5","8"],"answer":2}</t>
+Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node D to node F, including both endpoints.
+Answer: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["B","D","H"],"answer":2}</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Question: The directed graph has a unique shortest path from node 4 to node 2, following the direction of the arrows. How many edges are in that path?
+          <t>Look at the image with a labeled directed graph. Question: The directed graph has a unique shortest path from node D to node F, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the number of edges in that path as an integer.
+Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["4", "2"], "answer": 1}</t>
+          <t>{"evidence": ["D", "A", "G", "E", "F"], "answer": 4}</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>["4", "2"]</t>
+          <t>["D", "A", "G", "E", "F"]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -3623,16 +3323,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1399099983041354</v>
+        <v>1547067103965864</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0011.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0015.png</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0011.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0015.json</t>
         </is>
       </c>
     </row>
@@ -3649,17 +3349,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node E to node C, following the direction of the arrows. How many edges are in that path?
+          <t>Look at the image with a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node D to node E, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node C, including both endpoints.
-Answer rule: set "answer" to the number of edges in that path as an integer.
+Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node D to node E, including both endpoints.
+Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["B","D","H"],"answer":2}</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node E to node C, following the direction of the arrows. How many edges are in that path?
+          <t>Look at the image with a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node D to node E, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
@@ -3668,12 +3368,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["E", "G", "F", "B", "A", "C"], "answer": 5}</t>
+          <t>{"evidence": ["D", "E"], "answer": 1}</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>["E", "G", "F", "B", "A", "C"]</t>
+          <t>["D", "E"]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3687,16 +3387,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1794412546991728</v>
+        <v>1695968858385137</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0022.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0014.png</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0022.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0014.json</t>
         </is>
       </c>
     </row>
@@ -3713,9 +3413,9 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Work from the image with a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node E to node D, following the direction of the arrows. How many edges are in that path?
+          <t>The image shows a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node C to node G, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node D, including both endpoints.
+Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node C to node G, including both endpoints.
 Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["B","D","H"],"answer":2}</t>
@@ -3723,21 +3423,21 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Work from the image with a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node E to node D, following the direction of the arrows. How many edges are in that path?
+          <t>The image shows a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node C to node G, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of edges in that path as an integer.
+Answer format: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["E", "D"], "answer": 1}</t>
+          <t>{"evidence": ["C", "E", "F", "B", "A", "G"], "answer": 5}</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>["E", "D"]</t>
+          <t>["C", "E", "F", "B", "A", "G"]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3751,16 +3451,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2540760140258489</v>
+        <v>2454069538658750</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0003.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0007.png</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0003.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0007.json</t>
         </is>
       </c>
     </row>
@@ -3777,31 +3477,31 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. The directed graph has a unique shortest path from node 7 to node 4, following the direction of the arrows. How many edges are in that path?
+          <t>The image shows a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node G to node C, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node 7 to node 4, including both endpoints.
+Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node G to node C, including both endpoints.
 Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
-{"evidence":["2","5","8"],"answer":2}</t>
+{"evidence":["B","D","H"],"answer":2}</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. The directed graph has a unique shortest path from node 7 to node 4, following the direction of the arrows. How many edges are in that path?
+          <t>The image shows a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node G to node C, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of edges in that path as an integer.
+Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["7", "6", "1", "3", "5", "4"], "answer": 5}</t>
+          <t>{"evidence": ["G", "D", "E", "A", "C"], "answer": 4}</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>["7", "6", "1", "3", "5", "4"]</t>
+          <t>["G", "D", "E", "A", "C"]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3815,16 +3515,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2868473325368587</v>
+        <v>2692168406540821</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0004.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0016.png</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0004.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0016.json</t>
         </is>
       </c>
     </row>
@@ -3841,17 +3541,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. The directed graph has a unique shortest path from node E to node D, following the direction of the arrows. How many edges are in that path?
+          <t>The image shows a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node B to node A, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node D, including both endpoints.
-Answer format: set "answer" to the number of edges in that path as an integer.
+Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node B to node A, including both endpoints.
+Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["B","D","H"],"answer":2}</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. The directed graph has a unique shortest path from node E to node D, following the direction of the arrows. How many edges are in that path?
+          <t>The image shows a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node B to node A, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
@@ -3860,12 +3560,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["E", "G", "H", "I", "C", "D"], "answer": 5}</t>
+          <t>{"evidence": ["B", "C", "E", "G", "D", "A"], "answer": 5}</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>["E", "G", "H", "I", "C", "D"]</t>
+          <t>["B", "C", "E", "G", "D", "A"]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3879,16 +3579,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3130089129426398</v>
+        <v>2714955433777675</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0006.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0023.png</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0006.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0023.json</t>
         </is>
       </c>
     </row>
@@ -3905,31 +3605,31 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Look at the image with a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node 4 to node 3, following the direction of the arrows. How many edges are in that path?
+          <t>Look at the image with a labeled directed graph. Task: The directed graph has a unique shortest path from node 6 to node 4, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node 4 to node 3, including both endpoints.
-Answer: set "answer" to the number of edges in that path as an integer.
+Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node 6 to node 4, including both endpoints.
+Answer requirement: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["2","5","8"],"answer":2}</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Look at the image with a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node 4 to node 3, following the direction of the arrows. How many edges are in that path?
+          <t>Look at the image with a labeled directed graph. Task: The directed graph has a unique shortest path from node 6 to node 4, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of edges in that path as an integer.
+Answer format: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["4", "3"], "answer": 1}</t>
+          <t>{"evidence": ["6", "1", "4"], "answer": 2}</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>["4", "3"]</t>
+          <t>["6", "1", "4"]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3943,16 +3643,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>3430559372872467</v>
+        <v>2828318604666303</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0005.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0008.png</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0005.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0008.json</t>
         </is>
       </c>
     </row>
@@ -3969,17 +3669,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node F to node B, following the direction of the arrows. How many edges are in that path?
+          <t>The image shows a labeled directed graph. Task: The directed graph has a unique shortest path from node 8 to node 6, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node F to node B, including both endpoints.
-Answer: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
+Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node 8 to node 6, including both endpoints.
+Answer field: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node F to node B, following the direction of the arrows. How many edges are in that path?
+          <t>The image shows a labeled directed graph. Task: The directed graph has a unique shortest path from node 8 to node 6, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
@@ -3988,12 +3688,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["F", "D", "A", "G", "B"], "answer": 4}</t>
+          <t>{"evidence": ["8", "5", "1", "7", "4", "6"], "answer": 5}</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>["F", "D", "A", "G", "B"]</t>
+          <t>["8", "5", "1", "7", "4", "6"]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4007,16 +3707,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>4090663874293645</v>
+        <v>3059915970468545</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0000.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0001.png</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0000.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0001.json</t>
         </is>
       </c>
     </row>
@@ -4033,31 +3733,31 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Work from the image with a labeled directed graph. Task: The directed graph has a unique shortest path from node E to node A, following the direction of the arrows. How many edges are in that path?
+          <t>The image shows a labeled directed graph. The directed graph has a unique shortest path from node 6 to node 5, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node A, including both endpoints.
-Answer field: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
+Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node 6 to node 5, including both endpoints.
+Answer format: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Work from the image with a labeled directed graph. Task: The directed graph has a unique shortest path from node E to node A, following the direction of the arrows. How many edges are in that path?
+          <t>The image shows a labeled directed graph. The directed graph has a unique shortest path from node 6 to node 5, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of edges in that path as an integer.
+Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["E", "H", "B", "D", "G", "A"], "answer": 5}</t>
+          <t>{"evidence": ["6", "7", "3", "2", "4", "5"], "answer": 5}</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>["E", "H", "B", "D", "G", "A"]</t>
+          <t>["6", "7", "3", "2", "4", "5"]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4071,16 +3771,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4191378540217189</v>
+        <v>3367755832599191</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0001.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0000.png</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0001.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0000.json</t>
         </is>
       </c>
     </row>
@@ -4097,17 +3797,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Question: The directed graph has a unique shortest path from node C to node E, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. Task: The directed graph has a unique shortest path from node F to node E, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node C to node E, including both endpoints.
-Answer format: set "answer" to the number of edges in that path as an integer.
+Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node F to node E, including both endpoints.
+Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["B","D","H"],"answer":2}</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Question: The directed graph has a unique shortest path from node C to node E, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. Task: The directed graph has a unique shortest path from node F to node E, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
@@ -4116,12 +3816,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["C", "E"], "answer": 1}</t>
+          <t>{"evidence": ["F", "G", "C", "B", "D", "E"], "answer": 5}</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>["C", "E"]</t>
+          <t>["F", "G", "C", "B", "D", "E"]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4135,16 +3835,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>4799218656377394</v>
+        <v>4569298852781869</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0018.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0002.png</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0018.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0002.json</t>
         </is>
       </c>
     </row>
@@ -4161,9 +3861,9 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node 4 to node 1, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node 5 to node 7, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node 4 to node 1, including both endpoints.
+Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node 5 to node 7, including both endpoints.
 Answer requirement: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["2","5","8"],"answer":2}</t>
@@ -4171,21 +3871,21 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node 4 to node 1, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node 5 to node 7, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of edges in that path as an integer.
+Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["4", "2", "1"], "answer": 2}</t>
+          <t>{"evidence": ["5", "6", "2", "4", "7"], "answer": 4}</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>["4", "2", "1"]</t>
+          <t>["5", "6", "2", "4", "7"]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4199,16 +3899,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>5120814453041531</v>
+        <v>4598462160562987</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0012.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0003.png</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0012.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0003.json</t>
         </is>
       </c>
     </row>
@@ -4225,17 +3925,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Work from the image with a labeled directed graph. The directed graph has a unique shortest path from node 7 to node 4, following the direction of the arrows. How many edges are in that path?
+          <t>Use the image containing a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node 3 to node 2, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node 7 to node 4, including both endpoints.
-Answer rule: set "answer" to the number of edges in that path as an integer.
+Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node 3 to node 2, including both endpoints.
+Answer format: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["2","5","8"],"answer":2}</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Work from the image with a labeled directed graph. The directed graph has a unique shortest path from node 7 to node 4, following the direction of the arrows. How many edges are in that path?
+          <t>Use the image containing a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node 3 to node 2, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
@@ -4244,12 +3944,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["7", "5", "1", "4"], "answer": 3}</t>
+          <t>{"evidence": ["3", "4", "6", "2"], "answer": 3}</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>["7", "5", "1", "4"]</t>
+          <t>["3", "4", "6", "2"]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4263,16 +3963,16 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>5492810427175618</v>
+        <v>4973808947558448</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0009.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0006.png</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0009.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0006.json</t>
         </is>
       </c>
     </row>
@@ -4289,17 +3989,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node 4 to node 5, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node 6 to node 2, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node 4 to node 5, including both endpoints.
-Answer format: set "answer" to the number of edges in that path as an integer.
+Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node 6 to node 2, including both endpoints.
+Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["2","5","8"],"answer":2}</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node 4 to node 5, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node 6 to node 2, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
@@ -4308,12 +4008,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["4", "6", "1", "2", "3", "5"], "answer": 5}</t>
+          <t>{"evidence": ["6", "5", "2"], "answer": 2}</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>["4", "6", "1", "2", "3", "5"]</t>
+          <t>["6", "5", "2"]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4327,16 +4027,16 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>5495369453389523</v>
+        <v>5065558170888794</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0020.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0022.png</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0020.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0022.json</t>
         </is>
       </c>
     </row>
@@ -4353,31 +4053,31 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled directed graph. Task: The directed graph has a unique shortest path from node F to node G, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. The directed graph has a unique shortest path from node 3 to node 1, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node F to node G, including both endpoints.
-Answer: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
+Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node 3 to node 1, including both endpoints.
+Answer requirement: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled directed graph. Task: The directed graph has a unique shortest path from node F to node G, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. The directed graph has a unique shortest path from node 3 to node 1, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of edges in that path as an integer.
+Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["F", "A", "E", "D", "B", "G"], "answer": 5}</t>
+          <t>{"evidence": ["3", "7", "4", "6", "5", "1"], "answer": 5}</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>["F", "A", "E", "D", "B", "G"]</t>
+          <t>["3", "7", "4", "6", "5", "1"]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4391,16 +4091,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>5828616382190251</v>
+        <v>5426161019185097</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0016.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0004.png</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0016.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0004.json</t>
         </is>
       </c>
     </row>
@@ -4417,31 +4117,31 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node E to node F, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. The directed graph has a unique shortest path from node 3 to node 1, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node F, including both endpoints.
-Answer rule: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
+Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node 3 to node 1, including both endpoints.
+Answer requirement: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node E to node F, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. The directed graph has a unique shortest path from node 3 to node 1, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of edges in that path as an integer.
+Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["E", "C", "G", "A", "F"], "answer": 4}</t>
+          <t>{"evidence": ["3", "4", "2", "1"], "answer": 3}</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>["E", "C", "G", "A", "F"]</t>
+          <t>["3", "4", "2", "1"]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4455,16 +4155,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>5863189973371334</v>
+        <v>6793365724526744</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0015.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0012.png</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0015.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0012.json</t>
         </is>
       </c>
     </row>
@@ -4481,31 +4181,31 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Look at the image with a labeled directed graph. Question: The directed graph has a unique shortest path from node 1 to node 8, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. Task: The directed graph has a unique shortest path from node D to node H, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node 1 to node 8, including both endpoints.
-Answer field: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["2","5","8"],"answer":2}</t>
+Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node D to node H, including both endpoints.
+Answer: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["B","D","H"],"answer":2}</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Look at the image with a labeled directed graph. Question: The directed graph has a unique shortest path from node 1 to node 8, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. Task: The directed graph has a unique shortest path from node D to node H, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of edges in that path as an integer.
+Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["1", "9", "4", "7", "3", "8"], "answer": 5}</t>
+          <t>{"evidence": ["D", "B", "A", "G", "C", "H"], "answer": 5}</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>["1", "9", "4", "7", "3", "8"]</t>
+          <t>["D", "B", "A", "G", "C", "H"]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4519,16 +4219,16 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>5995315203590796</v>
+        <v>7915438310049264</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0017.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0024.png</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0017.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0024.json</t>
         </is>
       </c>
     </row>
@@ -4545,31 +4245,31 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. The directed graph has a unique shortest path from node E to node D, following the direction of the arrows. How many edges are in that path?
+          <t>Look at the image with a labeled directed graph. Question: The directed graph has a unique shortest path from node E to node D, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node D, including both endpoints.
-Answer requirement: set "answer" to the number of edges in that path as an integer.
+Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node D, including both endpoints.
+Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["B","D","H"],"answer":2}</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. The directed graph has a unique shortest path from node E to node D, following the direction of the arrows. How many edges are in that path?
+          <t>Look at the image with a labeled directed graph. Question: The directed graph has a unique shortest path from node E to node D, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of edges in that path as an integer.
+Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["E", "C", "D"], "answer": 2}</t>
+          <t>{"evidence": ["E", "C", "F", "B", "D"], "answer": 4}</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>["E", "C", "D"]</t>
+          <t>["E", "C", "F", "B", "D"]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -4583,16 +4283,16 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>6207835224220370</v>
+        <v>7989875412342523</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0002.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0011.png</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0002.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0011.json</t>
         </is>
       </c>
     </row>
@@ -4609,31 +4309,31 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Question: The directed graph has a unique shortest path from node H to node D, following the direction of the arrows. How many edges are in that path?
+          <t>Use the image containing a labeled directed graph. The directed graph has a unique shortest path from node H to node B, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node H to node D, including both endpoints.
-Answer field: set "answer" to the number of edges in that path as an integer.
+Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node H to node B, including both endpoints.
+Answer format: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["B","D","H"],"answer":2}</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Question: The directed graph has a unique shortest path from node H to node D, following the direction of the arrows. How many edges are in that path?
+          <t>Use the image containing a labeled directed graph. The directed graph has a unique shortest path from node H to node B, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of edges in that path as an integer.
+Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["H", "C", "B", "F", "G", "D"], "answer": 5}</t>
+          <t>{"evidence": ["H", "G", "E", "A", "D", "B"], "answer": 5}</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>["H", "C", "B", "F", "G", "D"]</t>
+          <t>["H", "G", "E", "A", "D", "B"]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -4647,16 +4347,16 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>6589595442330601</v>
+        <v>7998068990162906</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0007.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0021.png</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0007.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0021.json</t>
         </is>
       </c>
     </row>
@@ -4673,31 +4373,31 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node 3 to node 1, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. Question: The directed graph has a unique shortest path from node 9 to node 6, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node 3 to node 1, including both endpoints.
-Answer format: set "answer" to the number of edges in that path as an integer.
+Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node 9 to node 6, including both endpoints.
+Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["2","5","8"],"answer":2}</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Determine the answer: The directed graph has a unique shortest path from node 3 to node 1, following the direction of the arrows. How many edges are in that path?
+          <t>Work from the image with a labeled directed graph. Question: The directed graph has a unique shortest path from node 9 to node 6, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of edges in that path as an integer.
+Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["3", "2", "1"], "answer": 2}</t>
+          <t>{"evidence": ["9", "3", "5", "8", "6"], "answer": 4}</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>["3", "2", "1"]</t>
+          <t>["9", "3", "5", "8", "6"]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -4711,7 +4411,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>6619540465913426</v>
+        <v>8264518323625765</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -4737,9 +4437,9 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Question: The directed graph has a unique shortest path from node 4 to node 3, following the direction of the arrows. How many edges are in that path?
+          <t>You are given an image with a labeled directed graph. Task: The directed graph has a unique shortest path from node 2 to node 1, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node 4 to node 3, including both endpoints.
+Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node 2 to node 1, including both endpoints.
 Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["2","5","8"],"answer":2}</t>
@@ -4747,21 +4447,21 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Question: The directed graph has a unique shortest path from node 4 to node 3, following the direction of the arrows. How many edges are in that path?
+          <t>You are given an image with a labeled directed graph. Task: The directed graph has a unique shortest path from node 2 to node 1, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of edges in that path as an integer.
+Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["4", "3"], "answer": 1}</t>
+          <t>{"evidence": ["2", "6", "8", "5", "1"], "answer": 4}</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>["4", "3"]</t>
+          <t>["2", "6", "8", "5", "1"]</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -4775,16 +4475,16 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>6893220396541968</v>
+        <v>8331806442229905</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0010.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0020.png</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0010.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0020.json</t>
         </is>
       </c>
     </row>
@@ -4801,9 +4501,9 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Work from the image with a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node B to node E, following the direction of the arrows. How many edges are in that path?
+          <t>The image shows a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node E to node F, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node B to node E, including both endpoints.
+Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node F, including both endpoints.
 Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["B","D","H"],"answer":2}</t>
@@ -4811,21 +4511,21 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Work from the image with a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node B to node E, following the direction of the arrows. How many edges are in that path?
+          <t>The image shows a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node E to node F, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of edges in that path as an integer.
+Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["B", "A", "E"], "answer": 2}</t>
+          <t>{"evidence": ["E", "D", "F"], "answer": 2}</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>["B", "A", "E"]</t>
+          <t>["E", "D", "F"]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4839,16 +4539,16 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>7891212366457013</v>
+        <v>8393644243540926</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0024.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0019.png</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0024.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0019.json</t>
         </is>
       </c>
     </row>
@@ -4865,9 +4565,9 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node B to node E, following the direction of the arrows. How many edges are in that path?
+          <t>Use the image containing a labeled directed graph. Task: The directed graph has a unique shortest path from node E to node A, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node B to node E, including both endpoints.
+Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node A, including both endpoints.
 Answer format: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["B","D","H"],"answer":2}</t>
@@ -4875,21 +4575,21 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Answer this question: The directed graph has a unique shortest path from node B to node E, following the direction of the arrows. How many edges are in that path?
+          <t>Use the image containing a labeled directed graph. Task: The directed graph has a unique shortest path from node E to node A, following the direction of the arrows. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of edges in that path as an integer.
+Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["B", "E"], "answer": 1}</t>
+          <t>{"evidence": ["E", "G", "F", "B", "A"], "answer": 4}</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>["B", "E"]</t>
+          <t>["E", "G", "F", "B", "A"]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4903,16 +4603,16 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>8070563743978528</v>
+        <v>8850047831477749</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0008.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/directed_shortest_path_length/0018.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0008.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/directed_shortest_path_length/0018.json</t>
         </is>
       </c>
     </row>
@@ -5026,9 +4726,9 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node D to node B. How many edges are in that path?
+          <t>Look at the image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node E to node G. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node D to node B, including both endpoints.
+Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node G, including both endpoints.
 Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["B","D","H"],"answer":2}</t>
@@ -5036,21 +4736,21 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node D to node B. How many edges are in that path?
+          <t>Look at the image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node E to node G. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the number of edges in that path as an integer.
+Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["D", "H", "G", "E", "B"], "answer": 4}</t>
+          <t>{"evidence": ["E", "A", "D", "C", "G"], "answer": 4}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>["D", "H", "G", "E", "B"]</t>
+          <t>["E", "A", "D", "C", "G"]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -5064,16 +4764,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>69826338902015</v>
+        <v>228381514193301</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0012.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0024.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0012.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0024.json</t>
         </is>
       </c>
     </row>
@@ -5090,31 +4790,31 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node B to node F. How many edges are in that path?
+          <t>Use the image containing a labeled undirected graph. Question: The graph has a unique shortest path from node A to node B. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node B to node F, including both endpoints.
-Answer field: set "answer" to the number of edges in that path as an integer.
+Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node A to node B, including both endpoints.
+Answer format: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["B","D","H"],"answer":2}</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node B to node F. How many edges are in that path?
+          <t>Use the image containing a labeled undirected graph. Question: The graph has a unique shortest path from node A to node B. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of edges in that path as an integer.
+Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["B", "C", "I", "A", "H", "F"], "answer": 5}</t>
+          <t>{"evidence": ["A", "D", "B"], "answer": 2}</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>["B", "C", "I", "A", "H", "F"]</t>
+          <t>["A", "D", "B"]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -5128,16 +4828,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>287494933191654</v>
+        <v>551935400641206</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0002.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0004.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0002.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0004.json</t>
         </is>
       </c>
     </row>
@@ -5154,17 +4854,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node 9 to node 7. How many edges are in that path?
+          <t>Look at the image with a labeled undirected graph. Task: The graph has a unique shortest path from node 8 to node 2. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node 9 to node 7, including both endpoints.
-Answer field: set "answer" to the number of edges in that path as an integer.
+Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node 8 to node 2, including both endpoints.
+Answer requirement: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["2","5","8"],"answer":2}</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node 9 to node 7. How many edges are in that path?
+          <t>Look at the image with a labeled undirected graph. Task: The graph has a unique shortest path from node 8 to node 2. How many edges are in that path?
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the number of edges in that path as an integer.
 Example JSON:
@@ -5173,12 +4873,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["9", "5", "3", "8", "7"], "answer": 4}</t>
+          <t>{"evidence": ["8", "1", "5", "6", "7", "2"], "answer": 5}</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>["9", "5", "3", "8", "7"]</t>
+          <t>["8", "1", "5", "6", "7", "2"]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -5192,16 +4892,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>567530650124902</v>
+        <v>594343022204391</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0014.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0016.png</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0014.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0016.json</t>
         </is>
       </c>
     </row>
@@ -5218,31 +4918,31 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled undirected graph. Question: The graph has a unique shortest path from node 4 to node 6. How many edges are in that path?
+          <t>The image shows a labeled undirected graph. Task: The graph has a unique shortest path from node 8 to node 9. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node 4 to node 6, including both endpoints.
-Answer format: set "answer" to the number of edges in that path as an integer.
+Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node 8 to node 9, including both endpoints.
+Answer requirement: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["2","5","8"],"answer":2}</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled undirected graph. Question: The graph has a unique shortest path from node 4 to node 6. How many edges are in that path?
+          <t>The image shows a labeled undirected graph. Task: The graph has a unique shortest path from node 8 to node 9. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of edges in that path as an integer.
+Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["4", "7", "6"], "answer": 2}</t>
+          <t>{"evidence": ["8", "2", "5", "4", "9"], "answer": 4}</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>["4", "7", "6"]</t>
+          <t>["8", "2", "5", "4", "9"]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -5256,16 +4956,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>978948684731549</v>
+        <v>834807544620562</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0001.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0010.png</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0001.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0010.json</t>
         </is>
       </c>
     </row>
@@ -5282,31 +4982,31 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node E to node F. How many edges are in that path?
+          <t>Look at the image with a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node 3 to node 7. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node F, including both endpoints.
-Answer requirement: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
+Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node 3 to node 7, including both endpoints.
+Answer format: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node E to node F. How many edges are in that path?
+          <t>Look at the image with a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node 3 to node 7. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of edges in that path as an integer.
+Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["E", "A", "F"], "answer": 2}</t>
+          <t>{"evidence": ["3", "1", "2", "4", "5", "7"], "answer": 5}</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>["E", "A", "F"]</t>
+          <t>["3", "1", "2", "4", "5", "7"]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5320,16 +5020,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1024517416056068</v>
+        <v>844375122588781</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0000.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0013.png</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0000.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0013.json</t>
         </is>
       </c>
     </row>
@@ -5346,31 +5046,31 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Look at the image with a labeled undirected graph. Question: The graph has a unique shortest path from node 7 to node 4. How many edges are in that path?
+          <t>Work from the image with a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node 3 to node 8. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node 7 to node 4, including both endpoints.
+Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node 3 to node 8, including both endpoints.
+Answer: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node 3 to node 8. How many edges are in that path?
+Return a valid JSON object with key "answer".
 Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
-{"evidence":["2","5","8"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the image with a labeled undirected graph. Question: The graph has a unique shortest path from node 7 to node 4. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of edges in that path as an integer.
-Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["7", "1", "6", "4"], "answer": 3}</t>
+          <t>{"evidence": ["3", "7", "4", "1", "2", "8"], "answer": 5}</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>["7", "1", "6", "4"]</t>
+          <t>["3", "7", "4", "1", "2", "8"]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -5384,16 +5084,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1587661386879979</v>
+        <v>1315413479870284</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0006.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0014.png</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0006.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0014.json</t>
         </is>
       </c>
     </row>
@@ -5410,31 +5110,31 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node A to node C. How many edges are in that path?
+          <t>Look at the image with a labeled undirected graph. The graph has a unique shortest path from node 8 to node 4. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node A to node C, including both endpoints.
+Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node 8 to node 4, including both endpoints.
 Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
+{"evidence":["2","5","8"],"answer":2}</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node A to node C. How many edges are in that path?
+          <t>Look at the image with a labeled undirected graph. The graph has a unique shortest path from node 8 to node 4. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the number of edges in that path as an integer.
+Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["A", "I", "E", "B", "H", "C"], "answer": 5}</t>
+          <t>{"evidence": ["8", "3", "4"], "answer": 2}</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>["A", "I", "E", "B", "H", "C"]</t>
+          <t>["8", "3", "4"]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -5448,7 +5148,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1627780908905746</v>
+        <v>1316318335536687</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -5474,31 +5174,31 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled undirected graph. Question: The graph has a unique shortest path from node 3 to node 2. How many edges are in that path?
+          <t>The image shows a labeled undirected graph. The graph has a unique shortest path from node 5 to node 7. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node 3 to node 2, including both endpoints.
+Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node 5 to node 7, including both endpoints.
+Answer requirement: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled undirected graph. The graph has a unique shortest path from node 5 to node 7. How many edges are in that path?
+Return a valid JSON object with key "answer".
 Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
-{"evidence":["2","5","8"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Use the image containing a labeled undirected graph. Question: The graph has a unique shortest path from node 3 to node 2. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of edges in that path as an integer.
-Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["3", "2"], "answer": 1}</t>
+          <t>{"evidence": ["5", "8", "7"], "answer": 2}</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>["3", "2"]</t>
+          <t>["5", "8", "7"]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -5512,16 +5212,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1885537454812086</v>
+        <v>1446952582702935</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0015.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0022.png</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0015.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0022.json</t>
         </is>
       </c>
     </row>
@@ -5538,17 +5238,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled undirected graph. Question: The graph has a unique shortest path from node B to node H. How many edges are in that path?
+          <t>Work from the image with a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node A to node G. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node B to node H, including both endpoints.
-Answer requirement: set "answer" to the number of edges in that path as an integer.
+Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node A to node G, including both endpoints.
+Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["B","D","H"],"answer":2}</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled undirected graph. Question: The graph has a unique shortest path from node B to node H. How many edges are in that path?
+          <t>Work from the image with a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node A to node G. How many edges are in that path?
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the number of edges in that path as an integer.
 Example JSON:
@@ -5557,12 +5257,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["B", "H"], "answer": 1}</t>
+          <t>{"evidence": ["A", "F", "C", "G"], "answer": 3}</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>["B", "H"]</t>
+          <t>["A", "F", "C", "G"]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -5576,16 +5276,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1958367769138203</v>
+        <v>2598378416855485</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0005.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0001.png</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0005.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0001.json</t>
         </is>
       </c>
     </row>
@@ -5602,15 +5302,847 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>Work from the image with a labeled undirected graph. The graph has a unique shortest path from node B to node C. How many edges are in that path?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node B to node C, including both endpoints.
+Answer format: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["B","D","H"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled undirected graph. The graph has a unique shortest path from node B to node C. How many edges are in that path?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "E", "C"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>["B", "E", "C"]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>label_path</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2845403037660323</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0023.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="213.75" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_path_shortest_path_length</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>shortest_path_length</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node H to node I. How many edges are in that path?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node H to node I, including both endpoints.
+Answer requirement: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["B","D","H"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node H to node I. How many edges are in that path?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["H", "A", "F", "C", "I"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>["H", "A", "F", "C", "I"]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>label_path</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>3016843639198800</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0003.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="213.75" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_path_shortest_path_length</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>shortest_path_length</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node 7 to node 6. How many edges are in that path?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node 7 to node 6, including both endpoints.
+Answer requirement: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node 7 to node 6. How many edges are in that path?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["7", "5", "8", "2", "6"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>["7", "5", "8", "2", "6"]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>label_path</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>3417229307966731</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0017.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="213.75" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_path_shortest_path_length</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>shortest_path_length</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node 3 to node 4. How many edges are in that path?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node 3 to node 4, including both endpoints.
+Answer requirement: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node 3 to node 4. How many edges are in that path?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["3", "1", "4"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>["3", "1", "4"]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>label_path</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>3576099554418031</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0007.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="213.75" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_path_shortest_path_length</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>shortest_path_length</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node 1 to node 4. How many edges are in that path?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node 1 to node 4, including both endpoints.
+Answer format: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node 1 to node 4. How many edges are in that path?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "4"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>["1", "4"]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>label_path</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>3804269408041474</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0005.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="213.75" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_path_shortest_path_length</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>shortest_path_length</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled undirected graph. Question: The graph has a unique shortest path from node A to node E. How many edges are in that path?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node A to node E, including both endpoints.
+Answer format: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["B","D","H"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled undirected graph. Question: The graph has a unique shortest path from node A to node E. How many edges are in that path?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "B", "E"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>["A", "B", "E"]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>label_path</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>3969543396155262</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0015.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="213.75" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_path_shortest_path_length</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>shortest_path_length</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled undirected graph. Question: The graph has a unique shortest path from node E to node F. How many edges are in that path?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node F, including both endpoints.
+Answer rule: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["B","D","H"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled undirected graph. Question: The graph has a unique shortest path from node E to node F. How many edges are in that path?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["E", "A", "I", "G", "F"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>["E", "A", "I", "G", "F"]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>label_path</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>4019876453188196</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0002.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="213.75" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_path_shortest_path_length</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>shortest_path_length</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled undirected graph. Task: The graph has a unique shortest path from node D to node A. How many edges are in that path?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node D to node A, including both endpoints.
+Answer: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["B","D","H"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled undirected graph. Task: The graph has a unique shortest path from node D to node A. How many edges are in that path?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["D", "C", "A"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>["D", "C", "A"]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>label_path</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>4755507033126229</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0006.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="213.75" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_path_shortest_path_length</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>shortest_path_length</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled undirected graph. The graph has a unique shortest path from node 6 to node 9. How many edges are in that path?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node 6 to node 9, including both endpoints.
+Answer format: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled undirected graph. The graph has a unique shortest path from node 6 to node 9. How many edges are in that path?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["6", "8", "7", "9"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>["6", "8", "7", "9"]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>label_path</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5310006978660259</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0000.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="213.75" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_path_shortest_path_length</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>shortest_path_length</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled undirected graph. Question: The graph has a unique shortest path from node G to node C. How many edges are in that path?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node G to node C, including both endpoints.
+Answer requirement: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["B","D","H"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled undirected graph. Question: The graph has a unique shortest path from node G to node C. How many edges are in that path?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["G", "A", "C"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>["G", "A", "C"]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>label_path</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>5788378482129016</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0019.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="213.75" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_path_shortest_path_length</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>shortest_path_length</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled undirected graph. Task: The graph has a unique shortest path from node 5 to node 6. How many edges are in that path?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node 5 to node 6, including both endpoints.
+Answer: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled undirected graph. Task: The graph has a unique shortest path from node 5 to node 6. How many edges are in that path?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["5", "8", "4", "2", "6"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>["5", "8", "4", "2", "6"]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>label_path</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>5977685602845510</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0018.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="213.75" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_path_shortest_path_length</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>shortest_path_length</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled undirected graph. Question: The graph has a unique shortest path from node 6 to node 3. How many edges are in that path?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node 6 to node 3, including both endpoints.
+Answer: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled undirected graph. Question: The graph has a unique shortest path from node 6 to node 3. How many edges are in that path?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["6", "5", "4", "7", "1", "3"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>["6", "5", "4", "7", "1", "3"]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>label_path</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>7366514983577056</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0008.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="213.75" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_path_shortest_path_length</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>shortest_path_length</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Task: The graph has a unique shortest path from node 1 to node 3. How many edges are in that path?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node 1 to node 3, including both endpoints.
+Answer field: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"evidence":["2","5","8"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Task: The graph has a unique shortest path from node 1 to node 3. How many edges are in that path?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of edges in that path as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "4", "3"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>["1", "4", "3"]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>label_path</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>7794387627596051</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0009.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="213.75" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_path_shortest_path_length</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>shortest_path_length</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>Use the image containing a labeled undirected graph. Answer this question: The graph has a unique shortest path from node E to node D. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node D, including both endpoints.
-Answer rule: set "answer" to the number of edges in that path as an integer.
+Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node E to node D, including both endpoints.
+Answer format: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["B","D","H"],"answer":2}</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Use the image containing a labeled undirected graph. Answer this question: The graph has a unique shortest path from node E to node D. How many edges are in that path?
 Return a valid JSON object with key "answer".
@@ -5619,869 +6151,37 @@
 {"answer":2}</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["E", "C", "A", "B", "H", "D"], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>["E", "C", "A", "B", "H", "D"]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["E", "C", "D"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>["E", "C", "D"]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>label_path</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>2139355671446972</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0019.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="213.75" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_graph_path_shortest_path_length</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>shortest_path_length</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Work from the image with a labeled undirected graph. Question: The graph has a unique shortest path from node C to node E. How many edges are in that path?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node C to node E, including both endpoints.
-Answer requirement: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Work from the image with a labeled undirected graph. Question: The graph has a unique shortest path from node C to node E. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["C", "B", "E"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>["C", "B", "E"]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>label_path</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>2157752733137584</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0007.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="213.75" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_graph_path_shortest_path_length</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>shortest_path_length</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Use the image containing a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node 4 to node 9. How many edges are in that path?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node 4 to node 9, including both endpoints.
-Answer field: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["2","5","8"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Use the image containing a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node 4 to node 9. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["4", "5", "2", "3", "9"], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>["4", "5", "2", "3", "9"]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>label_path</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>2662612367580571</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0016.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="213.75" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_graph_path_shortest_path_length</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>shortest_path_length</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled undirected graph. Question: The graph has a unique shortest path from node D to node B. How many edges are in that path?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of the node labels along that unique shortest path in order from node D to node B, including both endpoints.
-Answer format: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled undirected graph. Question: The graph has a unique shortest path from node D to node B. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["D", "C", "A", "B"], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>["D", "C", "A", "B"]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>label_path</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>3378299497816872</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0021.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="213.75" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_graph_path_shortest_path_length</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>shortest_path_length</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node C to node F. How many edges are in that path?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node C to node F, including both endpoints.
-Answer: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node C to node F. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["C", "G", "D", "E", "B", "F"], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>["C", "G", "D", "E", "B", "F"]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>label_path</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>3495320869786125</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0017.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="213.75" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_graph_path_shortest_path_length</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>shortest_path_length</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with a labeled undirected graph. Question: The graph has a unique shortest path from node D to node F. How many edges are in that path?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node D to node F, including both endpoints.
-Answer field: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with a labeled undirected graph. Question: The graph has a unique shortest path from node D to node F. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["D", "C", "F"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>["D", "C", "F"]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>label_path</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>4132246070823665</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0023.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="213.75" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_graph_path_shortest_path_length</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>shortest_path_length</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Use the image containing a labeled undirected graph. Question: The graph has a unique shortest path from node C to node F. How many edges are in that path?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node C to node F, including both endpoints.
-Answer field: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Use the image containing a labeled undirected graph. Question: The graph has a unique shortest path from node C to node F. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["C", "E", "D", "F"], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>["C", "E", "D", "F"]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>label_path</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>4166621867048560</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0018.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0018.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="213.75" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_graph_path_shortest_path_length</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>shortest_path_length</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with a labeled undirected graph. Question: The graph has a unique shortest path from node 4 to node 5. How many edges are in that path?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node 4 to node 5, including both endpoints.
-Answer: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["2","5","8"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with a labeled undirected graph. Question: The graph has a unique shortest path from node 4 to node 5. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["4", "8", "5"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>["4", "8", "5"]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>label_path</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>4835092179086956</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0004.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="213.75" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_graph_path_shortest_path_length</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>shortest_path_length</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Look at the image with a labeled undirected graph. The graph has a unique shortest path from node 2 to node 6. How many edges are in that path?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node 2 to node 6, including both endpoints.
-Answer rule: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["2","5","8"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Look at the image with a labeled undirected graph. The graph has a unique shortest path from node 2 to node 6. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["2", "5", "6"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>["2", "5", "6"]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>label_path</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>5211887011907981</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0003.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="213.75" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_graph_path_shortest_path_length</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>shortest_path_length</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Look at the image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node G to node D. How many edges are in that path?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node G to node D, including both endpoints.
-Answer field: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Look at the image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node G to node D. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["G", "B", "A", "F", "C", "D"], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>["G", "B", "A", "F", "C", "D"]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>label_path</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>6101342776459671</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0022.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0022.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="213.75" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_graph_path_shortest_path_length</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>shortest_path_length</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Look at the image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node 1 to node 3. How many edges are in that path?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node 1 to node 3, including both endpoints.
-Answer: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["2","5","8"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Look at the image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node 1 to node 3. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["1", "3"], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>["1", "3"]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>label_path</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>6313417421342065</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0009.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0009.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="213.75" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_graph_path_shortest_path_length</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>shortest_path_length</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Look at the image with a labeled undirected graph. Task: The graph has a unique shortest path from node 1 to node 3. How many edges are in that path?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array of the node labels along that unique shortest path in order from node 1 to node 3, including both endpoints.
-Answer requirement: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["2","5","8"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Look at the image with a labeled undirected graph. Task: The graph has a unique shortest path from node 1 to node 3. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["1", "5", "3"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>["1", "5", "3"]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>label_path</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>6934512166832886</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0024.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="213.75" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_graph_path_shortest_path_length</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>shortest_path_length</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Work from the image with a labeled undirected graph. The graph has a unique shortest path from node B to node E. How many edges are in that path?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of the node labels along that unique shortest path in order from node B to node E, including both endpoints.
-Answer: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Work from the image with a labeled undirected graph. The graph has a unique shortest path from node B to node E. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "G", "C", "E"], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>["B", "G", "C", "E"]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>label_path</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>6943564838160649</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="K24" t="n">
+        <v>8372148931618337</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0011.png</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="213.75" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_graph_path_shortest_path_length</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>shortest_path_length</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Use the image containing a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node A to node B. How many edges are in that path?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node A to node B, including both endpoints.
-Answer field: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"evidence":["B","D","H"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Use the image containing a labeled undirected graph. Determine the answer: The graph has a unique shortest path from node A to node B. How many edges are in that path?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of edges in that path as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["A", "D", "F", "C", "B"], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>["A", "D", "F", "C", "B"]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>label_path</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>7072891607642842</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0010.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0010.json</t>
         </is>
       </c>
     </row>
@@ -6498,31 +6198,31 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Work from the image with a labeled undirected graph. Task: The graph has a unique shortest path from node D to node E. How many edges are in that path?
+          <t>You are given an image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node B to node A. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node D to node E, including both endpoints.
-Answer rule: set "answer" to the number of edges in that path as an integer.
+Evidence field: set "evidence" to an array of the node labels along that unique shortest path in order from node B to node A, including both endpoints.
+Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["B","D","H"],"answer":2}</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Work from the image with a labeled undirected graph. Task: The graph has a unique shortest path from node D to node E. How many edges are in that path?
+          <t>You are given an image with a labeled undirected graph. Answer this question: The graph has a unique shortest path from node B to node A. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of edges in that path as an integer.
+Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["D", "E"], "answer": 1}</t>
+          <t>{"evidence": ["B", "F", "I", "A"], "answer": 3}</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>["D", "E"]</t>
+          <t>["B", "F", "I", "A"]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6536,16 +6236,16 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>7229004203494598</v>
+        <v>8716225073166781</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0008.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0012.png</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0008.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0012.json</t>
         </is>
       </c>
     </row>
@@ -6562,9 +6262,9 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled undirected graph. Task: The graph has a unique shortest path from node 7 to node 6. How many edges are in that path?
+          <t>The image shows a labeled undirected graph. Question: The graph has a unique shortest path from node 7 to node 5. How many edges are in that path?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node 7 to node 6, including both endpoints.
+Evidence rule: set "evidence" to an array of the node labels along that unique shortest path in order from node 7 to node 5, including both endpoints.
 Answer rule: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"evidence":["2","5","8"],"answer":2}</t>
@@ -6572,21 +6272,21 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled undirected graph. Task: The graph has a unique shortest path from node 7 to node 6. How many edges are in that path?
+          <t>The image shows a labeled undirected graph. Question: The graph has a unique shortest path from node 7 to node 5. How many edges are in that path?
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of edges in that path as an integer.
+Answer field: set "answer" to the number of edges in that path as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["7", "1", "5", "9", "6"], "answer": 4}</t>
+          <t>{"evidence": ["7", "1", "2", "5"], "answer": 3}</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>["7", "1", "5", "9", "6"]</t>
+          <t>["7", "1", "2", "5"]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6600,16 +6300,16 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>7676248976707642</v>
+        <v>8827326595792712</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0013.png</t>
+          <t>graph/task_graph_path_shortest_path_length/images/shortest_path_length/0021.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0013.json</t>
+          <t>graph/task_graph_path_shortest_path_length/data/shortest_path_length/0021.json</t>
         </is>
       </c>
     </row>
